--- a/public/templates/process-docs/综合楼支架安装分项工程质量验收表.xlsx
+++ b/public/templates/process-docs/综合楼支架安装分项工程质量验收表.xlsx
@@ -105,7 +105,7 @@
         <rFont val="宋体"/>
         <family val="0"/>
       </rPr>
-      <t xml:space="preserve">5028G01-SG-ZHHC-01-01-05-001</t>
+      <t xml:space="preserve">{{文件编号}}</t>
     </r>
   </si>
   <si>
@@ -131,37 +131,37 @@
     <t xml:space="preserve">总承包单位</t>
   </si>
   <si>
-    <t xml:space="preserve">中核华辰建筑工程有限公司</t>
+    <t xml:space="preserve">{{施工单位}}</t>
   </si>
   <si>
     <t xml:space="preserve">项目负责人</t>
   </si>
   <si>
-    <t xml:space="preserve">谢智敏</t>
+    <t xml:space="preserve">{{施工单位项目负责人}}</t>
   </si>
   <si>
     <t xml:space="preserve">项目技术负责人</t>
   </si>
   <si>
-    <t xml:space="preserve">蒋志炜</t>
+    <t xml:space="preserve">{{总承包单位项目技术负责人}}</t>
   </si>
   <si>
     <t xml:space="preserve">施工单位</t>
   </si>
   <si>
-    <t xml:space="preserve">刘彦堂</t>
+    <t xml:space="preserve">{{施工单位项目技术负责人}}</t>
   </si>
   <si>
     <t xml:space="preserve">分包单位</t>
   </si>
   <si>
-    <t xml:space="preserve">河南誉华美建设工程有限公司</t>
+    <t xml:space="preserve">{{分包单位}}</t>
   </si>
   <si>
     <t xml:space="preserve">分包项目负责人</t>
   </si>
   <si>
-    <t xml:space="preserve">胡彦芳</t>
+    <t xml:space="preserve">{{分包单位项目负责人}}</t>
   </si>
   <si>
     <t xml:space="preserve">分包内容</t>
@@ -465,7 +465,7 @@
         <rFont val="宋体"/>
         <family val="0"/>
       </rPr>
-      <t xml:space="preserve">5028G01-SG-ZHHC-01-01-05-001</t>
+      <t xml:space="preserve">{{文件编号}}</t>
     </r>
     <r>
       <rPr>
